--- a/etf_holdings/2026-08-26_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.14%12,000,000</t>
+          <t>16.87%12,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.14%</t>
+          <t>16.87%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.63%1,690,000</t>
+          <t>5.80%1,690,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.80%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.94%1160</t>
+          <t>+6.95%3155</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+5.94%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1160</v>
+        <v>3155</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.51%8,460,000</t>
+          <t>5.79%3,150,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.79%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8460000</v>
+        <v>3150000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.95%3155</t>
+          <t>+5.94%1160</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3155</v>
+        <v>1160</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.44%3,100,000</t>
+          <t>5.71%8,460,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.71%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3100000</v>
+        <v>8460000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.69%2,110,000</t>
+          <t>4.85%2,110,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.85%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.46%60,000,000</t>
+          <t>4.31%60,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-10%5040</t>
+          <t>+9.99%5725</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+9.99%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5040</v>
+        <v>5725</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.67%1,100,000</t>
+          <t>3.62%1,087,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1100000</v>
+        <v>1087000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+9.99%5725</t>
+          <t>-10%5040</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+9.99%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5725</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.34%1,080,000</t>
+          <t>3.23%1,100,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1080000</v>
+        <v>1100000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.17%9,785,000</t>
+          <t>3.06%9,785,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,16 +1071,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.09%3,040,000</t>
+          <t>2.93%2,880,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3040000</v>
+        <v>2880000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.17%592</t>
+          <t>+1.23%2055</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>592</v>
+        <v>2055</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.81%8,000,000</t>
+          <t>2.76%2,307,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8000000</v>
+        <v>2307000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.23%2055</t>
+          <t>+0.17%592</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2055</v>
+        <v>592</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.79%2,307,000</t>
+          <t>2.76%8,000,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2307000</v>
+        <v>8000000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,20 +1254,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.41%630,000</t>
+          <t>2.61%660,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>630000</v>
+        <v>660000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.97%6290</t>
+          <t>+5.51%881</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>+5.51%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6290</v>
+        <v>881</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.13%626,000</t>
+          <t>2.33%4,550,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>626000</v>
+        <v>4550000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:46</t>
+          <t>2026-08-26 21:15:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.51%881</t>
+          <t>+9.97%6290</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+5.51%</t>
+          <t>+9.97%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>881</v>
+        <v>6290</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.11%4,250,000</t>
+          <t>2.29%626,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4250000</v>
+        <v>626000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,20 +1437,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.02%610,000</t>
+          <t>2.21%621,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>610000</v>
+        <v>621000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.82%2,640,000</t>
+          <t>1.81%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.88%15690</t>
+          <t>+3.03%1530</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15690</v>
+        <v>1530</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.64%179,500</t>
+          <t>1.69%1,900,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>179500</v>
+        <v>1900000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.16%949</t>
+          <t>+1.88%15690</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>949</v>
+        <v>15690</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.63%2,800,000</t>
+          <t>1.64%179,500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2800000</v>
+        <v>179500</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.60%15,000,000</t>
+          <t>1.58%15,000,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.03%1530</t>
+          <t>-3.16%949</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1530</v>
+        <v>949</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.59%1,800,000</t>
+          <t>1.55%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1800000</v>
+        <v>2800000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%1,200,000</t>
+          <t>1.40%1,200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.65%1195</t>
+          <t>+9.81%207</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+9.81%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1195</v>
+        <v>207</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.24%1,720,000</t>
+          <t>1.25%10,358,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1720000</v>
+        <v>10358000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.76%1980</t>
+          <t>-1.65%1195</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1980</v>
+        <v>1195</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.17%1,000,000</t>
+          <t>1.21%1,737,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1000000</v>
+        <v>1737000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.81%207</t>
+          <t>+0.76%1980</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.81%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>207</v>
+        <v>1980</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.12%10,000,000</t>
+          <t>1.15%1,000,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+4.57%286</t>
+          <t>+9.76%2025</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+4.57%</t>
+          <t>+9.76%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>286</v>
+        <v>2025</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.87%5,360,000</t>
+          <t>1.02%866,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5360000</v>
+        <v>866000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.76%2025</t>
+          <t>+4.57%286</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.76%</t>
+          <t>+4.57%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2025</v>
+        <v>286</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.86%780,000</t>
+          <t>0.89%5,360,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>780000</v>
+        <v>5360000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:47</t>
+          <t>2026-08-26 21:15:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.39%2,000,000</t>
+          <t>0.42%2,000,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.87%125.5</t>
+          <t>+6.93%741</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.87%</t>
+          <t>+6.93%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>125.5</v>
+        <v>741</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.33%4,500,000</t>
+          <t>0.35%800,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+6.93%741</t>
+          <t>+2.87%125.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+6.93%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>741</v>
+        <v>125.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.33%800,000</t>
+          <t>0.33%4,500,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>800000</v>
+        <v>4500000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,16 +2535,16 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.29%300,000</t>
+          <t>0.24%250,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.20%800,000</t>
+          <t>0.21%800,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.11%2,500,000</t>
+          <t>0.10%2,500,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:48</t>
+          <t>2026-08-26 21:15:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:50</t>
+          <t>2026-08-26 21:15:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:50</t>
+          <t>2026-08-26 21:15:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:50</t>
+          <t>2026-08-26 21:15:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:50</t>
+          <t>2026-08-26 21:15:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:50</t>
+          <t>2026-08-26 21:15:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:07</t>
+          <t>2026-08-26 21:38:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:08</t>
+          <t>2026-08-26 21:38:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:10</t>
+          <t>2026-08-26 21:38:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:11</t>
+          <t>2026-08-26 21:38:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:11</t>
+          <t>2026-08-26 21:38:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:11</t>
+          <t>2026-08-26 21:38:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:11</t>
+          <t>2026-08-26 21:38:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:11</t>
+          <t>2026-08-26 21:38:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:26</t>
+          <t>2026-08-26 22:19:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:27</t>
+          <t>2026-08-26 22:19:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:29</t>
+          <t>2026-08-26 22:19:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:30</t>
+          <t>2026-08-26 22:19:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:30</t>
+          <t>2026-08-26 22:19:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:30</t>
+          <t>2026-08-26 22:19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:30</t>
+          <t>2026-08-26 22:19:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:30</t>
+          <t>2026-08-26 22:19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
